--- a/branches/release/v2027.0.0-ballot/StructureDefinition-mii-pr-kardio-observation-rauchen.xlsx
+++ b/branches/release/v2027.0.0-ballot/StructureDefinition-mii-pr-kardio-observation-rauchen.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T14:03:30+00:00</t>
+    <t>2026-09-12T09:57:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
